--- a/Figure 1/Mouse weight & GTT/Weight&GTTCohort3.xlsx
+++ b/Figure 1/Mouse weight & GTT/Weight&GTTCohort3.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026-Human-Mice\Schoukroun-2026-Human-Mice\Figure 1\Mouse weight &amp; GTT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E6FACD-CA91-4D75-B19B-0DDD2A442EB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE6EE99E-FFFF-44FC-B52D-E080C336B674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A514A187-A7D1-4A2E-BBE9-38EB1CA0002D}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="37">
   <si>
     <t>Weight</t>
   </si>
@@ -145,6 +145,9 @@
   </si>
   <si>
     <t>Animal</t>
+  </si>
+  <si>
+    <t>182M2</t>
   </si>
 </sst>
 </file>
@@ -2984,7 +2987,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
         <v>14</v>
@@ -3290,7 +3293,7 @@
         <v>11</v>
       </c>
       <c r="B29" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C29" t="s">
         <v>14</v>
@@ -3596,7 +3599,7 @@
         <v>11</v>
       </c>
       <c r="B47" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C47" t="s">
         <v>14</v>
@@ -3902,7 +3905,7 @@
         <v>11</v>
       </c>
       <c r="B65" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
@@ -4208,7 +4211,7 @@
         <v>11</v>
       </c>
       <c r="B83" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C83" t="s">
         <v>14</v>
@@ -4514,7 +4517,7 @@
         <v>11</v>
       </c>
       <c r="B101" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C101" t="s">
         <v>14</v>

--- a/Figure 1/Mouse weight & GTT/Weight&GTTCohort3.xlsx
+++ b/Figure 1/Mouse weight & GTT/Weight&GTTCohort3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\florians\Documents\GitHub\Schoukroun2026-Human-Mice\Schoukroun-2026-Human-Mice\Figure 1\Mouse weight &amp; GTT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE6EE99E-FFFF-44FC-B52D-E080C336B674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C017FB-03D5-4233-A61A-086FA8940B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A514A187-A7D1-4A2E-BBE9-38EB1CA0002D}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="689" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="37">
   <si>
     <t>Weight</t>
   </si>
@@ -147,7 +147,7 @@
     <t>Animal</t>
   </si>
   <si>
-    <t>182M2</t>
+    <t>182M1</t>
   </si>
 </sst>
 </file>
@@ -2809,14 +2809,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2351EE4F-5BCF-49F0-BB77-4C4BF594B1E4}">
-  <dimension ref="A1:E121"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>35</v>
       </c>
       <c r="C1" t="s">
@@ -2831,53 +2831,53 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>113</v>
+        <v>325</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
       <c r="E3">
-        <v>89</v>
+        <v>441</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E4">
-        <v>104</v>
+        <v>600</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -2885,58 +2885,58 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E5">
-        <v>203</v>
+        <v>600</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E6">
-        <v>178</v>
+        <v>600</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E7">
-        <v>96</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
@@ -2945,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>129</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -2953,67 +2953,67 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
         <v>9</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E9">
-        <v>256</v>
+        <v>547</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E10">
-        <v>131</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E11">
-        <v>94</v>
+        <v>584</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
         <v>9</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E12">
-        <v>117</v>
+        <v>600</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -3021,67 +3021,67 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
         <v>9</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E13">
-        <v>325</v>
+        <v>492</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>112</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E15">
-        <v>98</v>
+        <v>511</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
         <v>9</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="E16">
-        <v>176</v>
+        <v>600</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -3089,101 +3089,101 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
         <v>9</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E17">
-        <v>246</v>
+        <v>600</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="E18">
-        <v>134</v>
+        <v>600</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="E19">
-        <v>112</v>
+        <v>489</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C20" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D20">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>332</v>
+        <v>256</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D21">
         <v>15</v>
       </c>
       <c r="E21">
-        <v>351</v>
+        <v>600</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
         <v>9</v>
       </c>
       <c r="D22">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E22">
-        <v>413</v>
+        <v>600</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -3191,50 +3191,50 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C23" t="s">
         <v>9</v>
       </c>
       <c r="D23">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="E23">
-        <v>511</v>
+        <v>600</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C24" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D24">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="E24">
-        <v>350</v>
+        <v>542</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C25" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D25">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="E25">
-        <v>413</v>
+        <v>449</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -3242,24 +3242,24 @@
         <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C26" t="s">
         <v>9</v>
       </c>
       <c r="D26">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>487</v>
+        <v>117</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C27" t="s">
         <v>9</v>
@@ -3268,41 +3268,41 @@
         <v>15</v>
       </c>
       <c r="E27">
-        <v>600</v>
+        <v>539</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B28" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D28">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E28">
-        <v>370</v>
+        <v>350</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C29" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D29">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="E29">
-        <v>207</v>
+        <v>373</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -3310,67 +3310,67 @@
         <v>10</v>
       </c>
       <c r="B30" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C30" t="s">
         <v>9</v>
       </c>
       <c r="D30">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="E30">
-        <v>539</v>
+        <v>251</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C31" t="s">
         <v>9</v>
       </c>
       <c r="D31">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="E31">
-        <v>441</v>
+        <v>241</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B32" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D32">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>265</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D33">
         <v>15</v>
       </c>
       <c r="E33">
-        <v>338</v>
+        <v>537</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -3384,95 +3384,95 @@
         <v>9</v>
       </c>
       <c r="D34">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E34">
-        <v>537</v>
+        <v>600</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B35" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C35" t="s">
         <v>9</v>
       </c>
       <c r="D35">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="E35">
-        <v>547</v>
+        <v>600</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C36" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D36">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="E36">
-        <v>252</v>
+        <v>600</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C37" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D37">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="E37">
-        <v>315</v>
+        <v>600</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C38" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D38">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>339</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B39" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39">
         <v>15</v>
       </c>
-      <c r="C39" t="s">
-        <v>14</v>
-      </c>
-      <c r="D39">
-        <v>30</v>
-      </c>
       <c r="E39">
-        <v>383</v>
+        <v>413</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -3494,53 +3494,53 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B41" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C41" t="s">
         <v>9</v>
       </c>
       <c r="D41">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E41">
-        <v>600</v>
+        <v>327</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B42" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D42">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="E42">
-        <v>374</v>
+        <v>270</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B43" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C43" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D43">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="E43">
-        <v>336</v>
+        <v>216</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -3554,61 +3554,61 @@
         <v>9</v>
       </c>
       <c r="D44">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E44">
-        <v>417</v>
+        <v>129</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B45" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C45" t="s">
         <v>9</v>
       </c>
       <c r="D45">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E45">
-        <v>600</v>
+        <v>487</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B46" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C46" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D46">
         <v>30</v>
       </c>
       <c r="E46">
-        <v>405</v>
+        <v>417</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B47" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="C47" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D47">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E47">
-        <v>206</v>
+        <v>430</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -3616,50 +3616,50 @@
         <v>10</v>
       </c>
       <c r="B48" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C48" t="s">
         <v>9</v>
       </c>
       <c r="D48">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="E48">
-        <v>350</v>
+        <v>334</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B49" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C49" t="s">
         <v>9</v>
       </c>
       <c r="D49">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="E49">
-        <v>600</v>
+        <v>302</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B50" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C50" t="s">
         <v>14</v>
       </c>
       <c r="D50">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E50">
-        <v>213</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -3667,67 +3667,67 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C51" t="s">
         <v>14</v>
       </c>
       <c r="D51">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E51">
-        <v>337</v>
+        <v>351</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B52" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C52" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D52">
         <v>30</v>
       </c>
       <c r="E52">
-        <v>600</v>
+        <v>383</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B53" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C53" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D53">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E53">
-        <v>600</v>
+        <v>366</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B54" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C54" t="s">
         <v>14</v>
       </c>
       <c r="D54">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="E54">
-        <v>245</v>
+        <v>252</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -3735,33 +3735,33 @@
         <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
       </c>
       <c r="D55">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="E55">
-        <v>356</v>
+        <v>186</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B56" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C56" t="s">
         <v>14</v>
       </c>
       <c r="D56">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E56">
-        <v>288</v>
+        <v>96</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -3769,67 +3769,67 @@
         <v>11</v>
       </c>
       <c r="B57" t="s">
+        <v>20</v>
+      </c>
+      <c r="C57" t="s">
+        <v>14</v>
+      </c>
+      <c r="D57">
         <v>15</v>
       </c>
-      <c r="C57" t="s">
-        <v>14</v>
-      </c>
-      <c r="D57">
-        <v>60</v>
-      </c>
       <c r="E57">
-        <v>366</v>
+        <v>413</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B58" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C58" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D58">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E58">
-        <v>327</v>
+        <v>336</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B59" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C59" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D59">
         <v>60</v>
       </c>
       <c r="E59">
-        <v>600</v>
+        <v>217</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B60" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
       </c>
       <c r="D60">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E60">
-        <v>253</v>
+        <v>180</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -3843,61 +3843,61 @@
         <v>14</v>
       </c>
       <c r="D61">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E61">
-        <v>217</v>
+        <v>133</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B62" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C62" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D62">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E62">
-        <v>430</v>
+        <v>94</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B63" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C63" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D63">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E63">
-        <v>600</v>
+        <v>207</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B64" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
       </c>
       <c r="D64">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E64">
-        <v>420</v>
+        <v>206</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -3905,7 +3905,7 @@
         <v>11</v>
       </c>
       <c r="B65" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
@@ -3919,53 +3919,53 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B66" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C66" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D66">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E66">
-        <v>373</v>
+        <v>212</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B67" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C67" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D67">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E67">
-        <v>600</v>
+        <v>182</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B68" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C68" t="s">
         <v>14</v>
       </c>
       <c r="D68">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="E68">
-        <v>162</v>
+        <v>98</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -3973,67 +3973,67 @@
         <v>11</v>
       </c>
       <c r="B69" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C69" t="s">
         <v>14</v>
       </c>
       <c r="D69">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="E69">
-        <v>258</v>
+        <v>338</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B70" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C70" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D70">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E70">
-        <v>600</v>
+        <v>337</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B71" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C71" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D71">
         <v>60</v>
       </c>
       <c r="E71">
-        <v>584</v>
+        <v>258</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B72" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C72" t="s">
         <v>14</v>
       </c>
       <c r="D72">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="E72">
-        <v>234</v>
+        <v>279</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -4041,33 +4041,33 @@
         <v>11</v>
       </c>
       <c r="B73" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C73" t="s">
         <v>14</v>
       </c>
       <c r="D73">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="E73">
-        <v>264</v>
+        <v>184</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B74" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C74" t="s">
         <v>14</v>
       </c>
       <c r="D74">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E74">
-        <v>241</v>
+        <v>112</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -4075,58 +4075,58 @@
         <v>11</v>
       </c>
       <c r="B75" t="s">
+        <v>25</v>
+      </c>
+      <c r="C75" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75">
         <v>15</v>
       </c>
-      <c r="C75" t="s">
-        <v>14</v>
-      </c>
-      <c r="D75">
-        <v>90</v>
-      </c>
       <c r="E75">
-        <v>252</v>
+        <v>315</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B76" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C76" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D76">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="E76">
-        <v>270</v>
+        <v>356</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B77" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C77" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D77">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="E77">
-        <v>600</v>
+        <v>264</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B78" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C78" t="s">
         <v>14</v>
@@ -4135,7 +4135,7 @@
         <v>90</v>
       </c>
       <c r="E78">
-        <v>188</v>
+        <v>217</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -4143,50 +4143,50 @@
         <v>11</v>
       </c>
       <c r="B79" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C79" t="s">
         <v>14</v>
       </c>
       <c r="D79">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E79">
-        <v>180</v>
+        <v>183</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C80" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D80">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E80">
-        <v>334</v>
+        <v>113</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C81" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D81">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="E81">
-        <v>542</v>
+        <v>332</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -4194,67 +4194,67 @@
         <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C82" t="s">
         <v>14</v>
       </c>
       <c r="D82">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="E82">
-        <v>286</v>
+        <v>339</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C83" t="s">
         <v>14</v>
       </c>
       <c r="D83">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="E83">
-        <v>212</v>
+        <v>288</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C84" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D84">
         <v>90</v>
       </c>
       <c r="E84">
-        <v>251</v>
+        <v>241</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C85" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D85">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E85">
-        <v>600</v>
+        <v>213</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -4262,67 +4262,67 @@
         <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C86" t="s">
         <v>14</v>
       </c>
       <c r="D86">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="E86">
-        <v>147</v>
+        <v>178</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C87" t="s">
         <v>14</v>
       </c>
       <c r="D87">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="E87">
-        <v>279</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C88" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D88">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="E88">
-        <v>600</v>
+        <v>374</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C89" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D89">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="E89">
-        <v>600</v>
+        <v>253</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -4330,7 +4330,7 @@
         <v>12</v>
       </c>
       <c r="B90" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="C90" t="s">
         <v>14</v>
@@ -4339,24 +4339,24 @@
         <v>90</v>
       </c>
       <c r="E90">
-        <v>231</v>
+        <v>188</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C91" t="s">
         <v>14</v>
       </c>
       <c r="D91">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E91">
-        <v>217</v>
+        <v>165</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -4364,67 +4364,67 @@
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C92" t="s">
         <v>14</v>
       </c>
       <c r="D92">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="E92">
-        <v>213</v>
+        <v>131</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B93" t="s">
+        <v>32</v>
+      </c>
+      <c r="C93" t="s">
+        <v>14</v>
+      </c>
+      <c r="D93">
         <v>15</v>
       </c>
-      <c r="C93" t="s">
-        <v>14</v>
-      </c>
-      <c r="D93">
-        <v>120</v>
-      </c>
       <c r="E93">
-        <v>186</v>
+        <v>370</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C94" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D94">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="E94">
-        <v>216</v>
+        <v>405</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C95" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D95">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E95">
-        <v>489</v>
+        <v>420</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -4432,24 +4432,24 @@
         <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="C96" t="s">
         <v>14</v>
       </c>
       <c r="D96">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E96">
-        <v>165</v>
+        <v>286</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="C97" t="s">
         <v>14</v>
@@ -4458,41 +4458,41 @@
         <v>120</v>
       </c>
       <c r="E97">
-        <v>133</v>
+        <v>240</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C98" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D98">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="E98">
-        <v>302</v>
+        <v>112</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C99" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D99">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="E99">
-        <v>449</v>
+        <v>265</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -4500,67 +4500,67 @@
         <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C100" t="s">
         <v>14</v>
       </c>
       <c r="D100">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="E100">
-        <v>240</v>
+        <v>213</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B101" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C101" t="s">
         <v>14</v>
       </c>
       <c r="D101">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E101">
-        <v>572</v>
+        <v>162</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C102" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D102">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E102">
-        <v>241</v>
+        <v>147</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C103" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D103">
         <v>120</v>
       </c>
       <c r="E103">
-        <v>600</v>
+        <v>131</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -4568,67 +4568,67 @@
         <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C104" t="s">
         <v>14</v>
       </c>
       <c r="D104">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="E104">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C105" t="s">
         <v>14</v>
       </c>
       <c r="D105">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="E105">
-        <v>184</v>
+        <v>252</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C106" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D106">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="E106">
-        <v>600</v>
+        <v>245</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C107" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D107">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E107">
-        <v>492</v>
+        <v>234</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -4642,18 +4642,18 @@
         <v>14</v>
       </c>
       <c r="D108">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="E108">
-        <v>196</v>
+        <v>231</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C109" t="s">
         <v>14</v>
@@ -4662,211 +4662,7 @@
         <v>120</v>
       </c>
       <c r="E109">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>11</v>
-      </c>
-      <c r="B110" t="s">
-        <v>24</v>
-      </c>
-      <c r="C110" t="s">
-        <v>14</v>
-      </c>
-      <c r="D110">
-        <v>0</v>
-      </c>
-      <c r="E110">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>11</v>
-      </c>
-      <c r="B111" t="s">
-        <v>24</v>
-      </c>
-      <c r="C111" t="s">
-        <v>14</v>
-      </c>
-      <c r="D111">
-        <v>15</v>
-      </c>
-      <c r="E111">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>11</v>
-      </c>
-      <c r="B112" t="s">
-        <v>24</v>
-      </c>
-      <c r="C112" t="s">
-        <v>14</v>
-      </c>
-      <c r="D112">
-        <v>30</v>
-      </c>
-      <c r="E112">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>11</v>
-      </c>
-      <c r="B113" t="s">
-        <v>24</v>
-      </c>
-      <c r="C113" t="s">
-        <v>14</v>
-      </c>
-      <c r="D113">
-        <v>60</v>
-      </c>
-      <c r="E113">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>11</v>
-      </c>
-      <c r="B114" t="s">
-        <v>24</v>
-      </c>
-      <c r="C114" t="s">
-        <v>14</v>
-      </c>
-      <c r="D114">
-        <v>90</v>
-      </c>
-      <c r="E114">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>11</v>
-      </c>
-      <c r="B115" t="s">
-        <v>24</v>
-      </c>
-      <c r="C115" t="s">
-        <v>14</v>
-      </c>
-      <c r="D115">
-        <v>120</v>
-      </c>
-      <c r="E115">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>12</v>
-      </c>
-      <c r="B116" t="s">
-        <v>32</v>
-      </c>
-      <c r="C116" t="s">
-        <v>14</v>
-      </c>
-      <c r="D116">
-        <v>0</v>
-      </c>
-      <c r="E116">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>12</v>
-      </c>
-      <c r="B117" t="s">
-        <v>32</v>
-      </c>
-      <c r="C117" t="s">
-        <v>14</v>
-      </c>
-      <c r="D117">
-        <v>15</v>
-      </c>
-      <c r="E117">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>12</v>
-      </c>
-      <c r="B118" t="s">
-        <v>32</v>
-      </c>
-      <c r="C118" t="s">
-        <v>14</v>
-      </c>
-      <c r="D118">
-        <v>30</v>
-      </c>
-      <c r="E118">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>12</v>
-      </c>
-      <c r="B119" t="s">
-        <v>32</v>
-      </c>
-      <c r="C119" t="s">
-        <v>14</v>
-      </c>
-      <c r="D119">
-        <v>60</v>
-      </c>
-      <c r="E119">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>12</v>
-      </c>
-      <c r="B120" t="s">
-        <v>32</v>
-      </c>
-      <c r="C120" t="s">
-        <v>14</v>
-      </c>
-      <c r="D120">
-        <v>90</v>
-      </c>
-      <c r="E120">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>12</v>
-      </c>
-      <c r="B121" t="s">
-        <v>32</v>
-      </c>
-      <c r="C121" t="s">
-        <v>14</v>
-      </c>
-      <c r="D121">
-        <v>120</v>
-      </c>
-      <c r="E121">
-        <v>240</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
